--- a/Planering 2026 LGIF.xlsx
+++ b/Planering 2026 LGIF.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b03121f1c8fff4a1/Barnen/Fotboll/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="13_ncr:1_{162264C3-A86B-4EBF-9E05-4244304888EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6984F25-7942-4ED3-A3CD-B2A8F02F8168}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="13_ncr:1_{162264C3-A86B-4EBF-9E05-4244304888EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9B46725-FCE6-4BA8-BCAF-68DB35CECA45}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-13935" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Matcher" sheetId="2" r:id="rId1"/>
@@ -18,8 +18,19 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Matcher!$A$1:$O$64</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="Rkc3BdRBUvpzEdKFgdgLjlOsjoi0xw9g4pNOhHK2JUo="/>
     </ext>
@@ -59,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="126">
   <si>
     <t>Datum</t>
   </si>
@@ -79,21 +90,6 @@
     <t>VIT-SVART</t>
   </si>
   <si>
-    <t>Onsdag</t>
-  </si>
-  <si>
-    <t>Tisdag</t>
-  </si>
-  <si>
-    <t>Fredag</t>
-  </si>
-  <si>
-    <t>Lördag</t>
-  </si>
-  <si>
-    <t>Torsdag</t>
-  </si>
-  <si>
     <t>ALLA TRE (DAM+VIT+SVART)</t>
   </si>
   <si>
@@ -139,9 +135,6 @@
     <t>Ansvarig</t>
   </si>
   <si>
-    <t>Söndag</t>
-  </si>
-  <si>
     <t>Dam</t>
   </si>
   <si>
@@ -163,9 +156,6 @@
     <t>Tvååkers IF (D4D)</t>
   </si>
   <si>
-    <t xml:space="preserve">Fredag </t>
-  </si>
-  <si>
     <t>Svart</t>
   </si>
   <si>
@@ -440,9 +430,6 @@
   </si>
   <si>
     <t>HC flyttad Båt 17:05_ 20:30</t>
-  </si>
-  <si>
-    <t>Måndag</t>
   </si>
   <si>
     <t>F16</t>
@@ -921,14 +908,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q1004"/>
   <sheetFormatPr defaultColWidth="14.3984375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="4" width="10" customWidth="1"/>
+    <col min="2" max="2" width="10.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="32" customWidth="1"/>
     <col min="6" max="7" width="10" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
@@ -949,75 +937,76 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="14.25" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="14.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>46089</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>26</v>
+      <c r="B2" s="3" t="str">
+        <f>IF(A2="","",CHOOSE(WEEKDAY(A2,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
+        <v>Söndag</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="3" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
@@ -1025,27 +1014,28 @@
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
     </row>
-    <row r="3" spans="1:17" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:17" ht="14.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>46093</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>10</v>
+      <c r="B3" s="3" t="str">
+        <f t="shared" ref="B3:B64" si="0">IF(A3="","",CHOOSE(WEEKDAY(A3,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
+        <v>Torsdag</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="3" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="3" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
@@ -1058,24 +1048,25 @@
       <c r="A4" s="2">
         <v>46094</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>34</v>
+      <c r="B4" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Fredag</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="3" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
@@ -1087,23 +1078,24 @@
       <c r="A5" s="2">
         <v>46096</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>26</v>
+      <c r="B5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Söndag</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="3" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
@@ -1116,23 +1108,24 @@
       <c r="A6" s="2">
         <v>46109</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>9</v>
+      <c r="B6" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Lördag</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="3" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
@@ -1141,21 +1134,22 @@
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
     </row>
-    <row r="7" spans="1:17" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:17" ht="14.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
         <v>46112</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>7</v>
+      <c r="B7" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Tisdag</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F7" s="3">
         <v>60220006</v>
@@ -1164,13 +1158,13 @@
         <v>1</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="K7" s="3" t="b">
         <v>1</v>
@@ -1184,17 +1178,18 @@
       <c r="A8" s="2">
         <v>46119</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>7</v>
+      <c r="B8" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Tisdag</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F8" s="3">
         <v>60713002</v>
@@ -1203,46 +1198,47 @@
         <v>1</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="K8" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="O8" s="3"/>
       <c r="P8" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="14.25" x14ac:dyDescent="0.45">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="14.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A9" s="2">
         <v>46120</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>6</v>
+      <c r="B9" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Onsdag</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F9" s="3">
         <v>60220007</v>
@@ -1251,42 +1247,43 @@
         <v>2</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K9" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A10" s="2">
         <v>46121</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>10</v>
+      <c r="B10" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Torsdag</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="F10" s="3">
         <v>60716004</v>
@@ -1295,42 +1292,43 @@
         <v>1</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="K10" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L10" s="4"/>
       <c r="M10" s="4" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="N10" s="4"/>
       <c r="O10" s="4"/>
       <c r="P10" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="14.25" x14ac:dyDescent="0.45">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="14.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A11" s="2">
         <v>46126</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>7</v>
+      <c r="B11" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Tisdag</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F11" s="3">
         <v>60220016</v>
@@ -1339,44 +1337,45 @@
         <v>3</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="K11" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="M11" s="3"/>
       <c r="N11" s="3" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="O11" s="3"/>
       <c r="P11" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A12" s="2">
         <v>46128</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>10</v>
+      <c r="B12" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Torsdag</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F12" s="3">
         <v>60713007</v>
@@ -1385,42 +1384,43 @@
         <v>2</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K12" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L12" s="4"/>
       <c r="M12" s="4" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
       <c r="P12" s="3" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A13" s="2">
         <v>46130</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
+      <c r="B13" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Lördag</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="F13" s="3">
         <v>60716005</v>
@@ -1429,25 +1429,25 @@
         <v>2</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K13" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="O13" s="3"/>
     </row>
@@ -1455,17 +1455,18 @@
       <c r="A14" s="2">
         <v>46134</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>6</v>
+      <c r="B14" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Onsdag</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="F14" s="3">
         <v>60713009</v>
@@ -1474,20 +1475,20 @@
         <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="K14" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L14" s="4"/>
       <c r="M14" s="4" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
@@ -1496,17 +1497,18 @@
       <c r="A15" s="2">
         <v>46136</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
+      <c r="B15" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Fredag</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="F15" s="3">
         <v>60716011</v>
@@ -1515,46 +1517,47 @@
         <v>3</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="K15" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="N15" s="3"/>
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" ht="14.25" x14ac:dyDescent="0.45">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="14.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A16" s="2">
         <v>46140</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>7</v>
+      <c r="B16" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Tisdag</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F16" s="3">
         <v>60220026</v>
@@ -1563,13 +1566,13 @@
         <v>5</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="K16" s="3" t="b">
         <v>1</v>
@@ -1584,17 +1587,18 @@
       <c r="A17" s="2">
         <v>46141</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>6</v>
+      <c r="B17" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Onsdag</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F17" s="3">
         <v>60713016</v>
@@ -1603,20 +1607,20 @@
         <v>4</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K17" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L17" s="4"/>
       <c r="M17" s="3" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="N17" s="4"/>
       <c r="O17" s="4"/>
@@ -1625,17 +1629,18 @@
       <c r="A18" s="2">
         <v>46144</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>9</v>
+      <c r="B18" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Lördag</v>
       </c>
       <c r="C18" s="6">
         <v>0.60416666666666663</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="F18" s="3">
         <v>60716014</v>
@@ -1644,39 +1649,40 @@
         <v>4</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K18" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L18" s="4"/>
       <c r="M18" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
     </row>
-    <row r="19" spans="1:16" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:16" ht="14.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A19" s="2">
         <v>46147</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>7</v>
+      <c r="B19" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Tisdag</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F19" s="3">
         <v>60220033</v>
@@ -1685,13 +1691,13 @@
         <v>6</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K19" s="3" t="b">
         <v>1</v>
@@ -1701,24 +1707,25 @@
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
       <c r="P19" s="3" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A20" s="2">
         <v>46148</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>6</v>
+      <c r="B20" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Onsdag</v>
       </c>
       <c r="C20" s="6">
         <v>0.82291666666666663</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="F20" s="3">
         <v>60716017</v>
@@ -1727,20 +1734,20 @@
         <v>5</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="K20" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L20" s="4"/>
       <c r="M20" s="3" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="N20" s="4"/>
       <c r="O20" s="4"/>
@@ -1749,17 +1756,18 @@
       <c r="A21" s="2">
         <v>46149</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>10</v>
+      <c r="B21" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Torsdag</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F21" s="3">
         <v>60713019</v>
@@ -1768,39 +1776,40 @@
         <v>5</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K21" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L21" s="4"/>
       <c r="M21" s="3" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="N21" s="4"/>
       <c r="O21" s="4"/>
     </row>
-    <row r="22" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="2">
         <v>46153</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>8</v>
+      <c r="B22" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Måndag</v>
       </c>
       <c r="C22" s="6">
         <v>0.82291666666666663</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F22" s="3">
         <v>60220020</v>
@@ -1809,19 +1818,19 @@
         <v>4</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K22" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
@@ -1831,17 +1840,18 @@
       <c r="A23" s="2">
         <v>46153</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>6</v>
+      <c r="B23" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Måndag</v>
       </c>
       <c r="C23" s="6">
         <v>0.84375</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F23" s="3">
         <v>60713024</v>
@@ -1850,44 +1860,45 @@
         <v>6</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="K23" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L23" s="4"/>
       <c r="M23" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="N23" s="4"/>
       <c r="O23" s="4" t="s">
         <v>4</v>
       </c>
       <c r="P23" s="4" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="2">
         <v>46157</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>8</v>
+      <c r="B24" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Fredag</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="F24" s="3">
         <v>60716023</v>
@@ -1896,42 +1907,43 @@
         <v>6</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K24" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L24" s="4"/>
       <c r="M24" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="N24" s="4"/>
       <c r="O24" s="4"/>
       <c r="P24" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="2">
         <v>46160</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>7</v>
+      <c r="B25" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Måndag</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F25" s="3">
         <v>60220046</v>
@@ -1940,13 +1952,13 @@
         <v>8</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K25" s="3" t="b">
         <v>1</v>
@@ -1960,17 +1972,18 @@
       <c r="A26" s="2">
         <v>46162</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>6</v>
+      <c r="B26" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Onsdag</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="F26" s="3">
         <v>60716027</v>
@@ -1979,20 +1992,20 @@
         <v>7</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="K26" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L26" s="4"/>
       <c r="M26" s="3" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="N26" s="4"/>
       <c r="O26" s="4"/>
@@ -2001,17 +2014,18 @@
       <c r="A27" s="2">
         <v>46163</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>10</v>
+      <c r="B27" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Torsdag</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F27" s="3">
         <v>60713027</v>
@@ -2020,20 +2034,20 @@
         <v>7</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K27" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L27" s="4"/>
       <c r="M27" s="3" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="N27" s="4"/>
       <c r="O27" s="4"/>
@@ -2042,17 +2056,18 @@
       <c r="A28" s="2">
         <v>46168</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>7</v>
+      <c r="B28" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Tisdag</v>
       </c>
       <c r="C28" s="6">
         <v>0.76041666666666663</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F28" s="3">
         <v>60713039</v>
@@ -2061,43 +2076,44 @@
         <v>10</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="K28" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="O28" s="3"/>
     </row>
-    <row r="29" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="2">
         <v>46170</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>10</v>
+      <c r="B29" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Torsdag</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F29" s="3">
         <v>60220052</v>
@@ -2106,13 +2122,13 @@
         <v>9</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="K29" s="3" t="b">
         <v>1</v>
@@ -2126,17 +2142,18 @@
       <c r="A30" s="2">
         <v>46171</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>8</v>
+      <c r="B30" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Fredag</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="F30" s="3">
         <v>60716032</v>
@@ -2145,39 +2162,40 @@
         <v>8</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K30" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L30" s="4"/>
       <c r="M30" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="N30" s="4"/>
       <c r="O30" s="4"/>
     </row>
-    <row r="31" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="2">
         <v>46175</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>7</v>
+      <c r="B31" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Tisdag</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F31" s="3">
         <v>60220060</v>
@@ -2186,13 +2204,13 @@
         <v>10</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K31" s="3" t="b">
         <v>1</v>
@@ -2206,17 +2224,18 @@
       <c r="A32" s="2">
         <v>46180</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>26</v>
+      <c r="B32" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Söndag</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F32" s="3">
         <v>60713035</v>
@@ -2225,47 +2244,48 @@
         <v>9</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K32" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L32" s="4"/>
       <c r="M32" s="3" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="N32" s="4"/>
       <c r="O32" s="4"/>
       <c r="P32" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="2">
         <v>46186</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>9</v>
+      <c r="B33" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Lördag</v>
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
@@ -2274,26 +2294,27 @@
       <c r="O33" s="3"/>
       <c r="P33" s="3"/>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="2">
         <v>46187</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>26</v>
+      <c r="B34" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Söndag</v>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
@@ -2302,26 +2323,27 @@
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="2">
         <v>46188</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>127</v>
+      <c r="B35" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Måndag</v>
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
@@ -2330,21 +2352,22 @@
       <c r="O35" s="3"/>
       <c r="P35" s="3"/>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="2">
         <v>46189</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>7</v>
+      <c r="B36" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Tisdag</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F36" s="3">
         <v>60220067</v>
@@ -2353,13 +2376,13 @@
         <v>12</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K36" s="3" t="b">
         <v>1</v>
@@ -2369,24 +2392,25 @@
       <c r="N36" s="4"/>
       <c r="O36" s="4"/>
       <c r="P36" s="3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="2">
         <v>46196</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>7</v>
+      <c r="B37" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Tisdag</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F37" s="3">
         <v>60220077</v>
@@ -2395,13 +2419,13 @@
         <v>13</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="K37" s="3" t="b">
         <v>1</v>
@@ -2411,24 +2435,25 @@
       <c r="N37" s="4"/>
       <c r="O37" s="4"/>
       <c r="P37" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="2">
         <v>46245</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>7</v>
+      <c r="B38" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Tisdag</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F38" s="3">
         <v>60220080</v>
@@ -2437,13 +2462,13 @@
         <v>14</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K38" s="3" t="b">
         <v>1</v>
@@ -2457,17 +2482,18 @@
       <c r="A39" s="9">
         <v>46252</v>
       </c>
-      <c r="B39" s="11" t="s">
-        <v>6</v>
+      <c r="B39" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>Tisdag</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="F39" s="11">
         <v>60716043</v>
@@ -2476,41 +2502,42 @@
         <v>11</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="K39" s="11" t="b">
         <v>1</v>
       </c>
       <c r="L39" s="13"/>
       <c r="M39" s="11" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="N39" s="13"/>
       <c r="O39" s="13"/>
       <c r="P39" s="7"/>
       <c r="Q39" s="7"/>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="2">
         <v>46257</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>26</v>
+      <c r="B40" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Söndag</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F40" s="3">
         <v>60220087</v>
@@ -2519,13 +2546,13 @@
         <v>15</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="K40" s="3" t="b">
         <v>1</v>
@@ -2535,24 +2562,25 @@
       <c r="N40" s="4"/>
       <c r="O40" s="4"/>
       <c r="P40" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="9">
-        <v>46259</v>
-      </c>
-      <c r="B41" s="11" t="s">
-        <v>7</v>
+        <v>46265</v>
+      </c>
+      <c r="B41" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>Måndag</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F41" s="11">
         <v>60220093</v>
@@ -2561,13 +2589,13 @@
         <v>16</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K41" s="11" t="b">
         <v>1</v>
@@ -2583,17 +2611,18 @@
       <c r="A42" s="2">
         <v>46260</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>6</v>
+      <c r="B42" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Onsdag</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F42" s="3">
         <v>60713048</v>
@@ -2602,20 +2631,20 @@
         <v>12</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="K42" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L42" s="4"/>
       <c r="M42" s="3" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="N42" s="4"/>
       <c r="O42" s="4"/>
@@ -2624,17 +2653,18 @@
       <c r="A43" s="2">
         <v>46261</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>10</v>
+      <c r="B43" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Torsdag</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="F43" s="3">
         <v>60716048</v>
@@ -2643,20 +2673,20 @@
         <v>12</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K43" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L43" s="4"/>
       <c r="M43" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="N43" s="4"/>
       <c r="O43" s="4"/>
@@ -2665,17 +2695,18 @@
       <c r="A44" s="2">
         <v>46266</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>6</v>
+      <c r="B44" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Tisdag</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="F44" s="3">
         <v>60716052</v>
@@ -2684,22 +2715,22 @@
         <v>13</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="K44" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="N44" s="3"/>
       <c r="O44" s="3"/>
@@ -2708,17 +2739,18 @@
       <c r="A45" s="2">
         <v>46267</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>6</v>
+      <c r="B45" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Onsdag</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F45" s="3">
         <v>60713051</v>
@@ -2727,41 +2759,42 @@
         <v>13</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K45" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="2">
         <v>46271</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>26</v>
+      <c r="B46" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Söndag</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F46" s="3">
         <v>60220097</v>
@@ -2770,13 +2803,13 @@
         <v>17</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="K46" s="3" t="b">
         <v>1</v>
@@ -2790,17 +2823,18 @@
       <c r="A47" s="2">
         <v>46273</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>10</v>
+      <c r="B47" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Tisdag</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="F47" s="3">
         <v>60716055</v>
@@ -2809,22 +2843,22 @@
         <v>14</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K47" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="N47" s="3"/>
       <c r="O47" s="3"/>
@@ -2833,17 +2867,18 @@
       <c r="A48" s="2">
         <v>46275</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>10</v>
+      <c r="B48" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Torsdag</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F48" s="3">
         <v>60713054</v>
@@ -2852,41 +2887,42 @@
         <v>14</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="K48" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" s="3"/>
     </row>
-    <row r="49" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" s="2">
-        <v>46281</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>6</v>
+        <v>46387</v>
+      </c>
+      <c r="B49" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Torsdag</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F49" s="3">
         <v>60220113</v>
@@ -2895,41 +2931,42 @@
         <v>19</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="K49" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="M49" s="3"/>
       <c r="N49" s="3"/>
       <c r="O49" s="3" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" s="2">
         <v>46281</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>6</v>
+      <c r="B50" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Onsdag</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F50" s="3">
         <v>60713060</v>
@@ -2938,43 +2975,44 @@
         <v>15</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="K50" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="N50" s="3"/>
       <c r="O50" s="3" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" s="2">
         <v>46283</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>7</v>
+      <c r="B51" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Fredag</v>
       </c>
       <c r="C51" s="6">
         <v>0.84375</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="F51" s="3">
         <v>60716058</v>
@@ -2983,41 +3021,42 @@
         <v>15</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="K51" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="N51" s="3"/>
       <c r="O51" s="3"/>
     </row>
-    <row r="52" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" s="2">
         <v>46287</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>7</v>
+      <c r="B52" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Tisdag</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F52" s="3">
         <v>60220119</v>
@@ -3026,13 +3065,13 @@
         <v>20</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K52" s="3" t="b">
         <v>1</v>
@@ -3044,19 +3083,20 @@
     </row>
     <row r="53" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A53" s="2">
-        <v>46289</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>10</v>
+        <v>46316</v>
+      </c>
+      <c r="B53" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Onsdag</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F53" s="3">
         <v>60713064</v>
@@ -3065,20 +3105,20 @@
         <v>16</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K53" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L53" s="4"/>
       <c r="M53" s="3" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="N53" s="4"/>
       <c r="O53" s="4"/>
@@ -3087,17 +3127,18 @@
       <c r="A54" s="2">
         <v>46290</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>8</v>
+      <c r="B54" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Fredag</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="F54" s="3">
         <v>60716062</v>
@@ -3106,39 +3147,40 @@
         <v>16</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K54" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L54" s="4"/>
       <c r="M54" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="N54" s="4"/>
       <c r="O54" s="4"/>
     </row>
-    <row r="55" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A55" s="2">
         <v>46295</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>6</v>
+      <c r="B55" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Onsdag</v>
       </c>
       <c r="C55" s="8">
         <v>0.84375</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F55" s="3">
         <v>60220066</v>
@@ -3147,19 +3189,19 @@
         <v>11</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="K55" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
@@ -3169,17 +3211,18 @@
       <c r="A56" s="2">
         <v>46297</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>8</v>
+      <c r="B56" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Fredag</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="F56" s="3">
         <v>60716068</v>
@@ -3188,22 +3231,22 @@
         <v>17</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="K56" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="N56" s="3"/>
       <c r="O56" s="3" t="s">
@@ -3214,17 +3257,18 @@
       <c r="A57" s="2">
         <v>46297</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>8</v>
+      <c r="B57" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Fredag</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F57" s="3">
         <v>60713066</v>
@@ -3233,43 +3277,44 @@
         <v>17</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="K57" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="N57" s="3"/>
       <c r="O57" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A58" s="2">
         <v>46299</v>
       </c>
-      <c r="B58" s="3" t="s">
-        <v>26</v>
+      <c r="B58" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Söndag</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F58" s="3">
         <v>60220122</v>
@@ -3278,13 +3323,13 @@
         <v>21</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="K58" s="3" t="b">
         <v>1</v>
@@ -3298,17 +3343,18 @@
       <c r="A59" s="2">
         <v>46301</v>
       </c>
-      <c r="B59" s="3" t="s">
-        <v>7</v>
+      <c r="B59" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Tisdag</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="F59" s="3">
         <v>60716069</v>
@@ -3317,20 +3363,20 @@
         <v>18</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K59" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L59" s="4"/>
       <c r="M59" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="N59" s="4"/>
       <c r="O59" s="4"/>
@@ -3339,17 +3385,18 @@
       <c r="A60" s="2">
         <v>46303</v>
       </c>
-      <c r="B60" s="3" t="s">
-        <v>10</v>
+      <c r="B60" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Torsdag</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F60" s="3">
         <v>60713071</v>
@@ -3358,39 +3405,40 @@
         <v>18</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I60" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J60" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="K60" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L60" s="4"/>
       <c r="M60" s="3" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="N60" s="4"/>
       <c r="O60" s="4"/>
     </row>
-    <row r="61" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A61" s="2">
         <v>46306</v>
       </c>
-      <c r="B61" s="3" t="s">
-        <v>26</v>
+      <c r="B61" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Söndag</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F61" s="3">
         <v>60220132</v>
@@ -3399,13 +3447,13 @@
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K61" s="3" t="b">
         <v>1</v>
@@ -3415,9 +3463,12 @@
       <c r="N61" s="4"/>
       <c r="O61" s="4"/>
     </row>
-    <row r="62" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A62" s="10"/>
-      <c r="B62" s="12"/>
+      <c r="B62" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="C62" s="12"/>
       <c r="D62" s="12"/>
       <c r="E62" s="12"/>
@@ -3432,9 +3483,12 @@
       <c r="N62" s="12"/>
       <c r="O62" s="12"/>
     </row>
-    <row r="63" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A63" s="2"/>
-      <c r="B63" s="3"/>
+      <c r="B63" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
@@ -3445,9 +3499,12 @@
       <c r="J63" s="3"/>
       <c r="K63" s="3"/>
     </row>
-    <row r="64" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="10"/>
-      <c r="B64" s="12"/>
+      <c r="B64" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="C64" s="12"/>
       <c r="D64" s="12"/>
       <c r="E64" s="12"/>
@@ -4404,6 +4461,12 @@
     <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <autoFilter ref="A1:O64" xr:uid="{00000000-0009-0000-0000-000001000000}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Svart"/>
+        <filter val="Vit"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O64">
       <sortCondition ref="A1:A64"/>
     </sortState>

--- a/Planering 2026 LGIF.xlsx
+++ b/Planering 2026 LGIF.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b03121f1c8fff4a1/Barnen/Fotboll/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="13_ncr:1_{162264C3-A86B-4EBF-9E05-4244304888EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9B46725-FCE6-4BA8-BCAF-68DB35CECA45}"/>
+  <xr:revisionPtr revIDLastSave="85" documentId="13_ncr:1_{162264C3-A86B-4EBF-9E05-4244304888EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AD55B4F-4592-4F62-8451-4D26691BFCD0}"/>
   <bookViews>
-    <workbookView xWindow="-13935" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Matcher" sheetId="2" r:id="rId1"/>
@@ -547,7 +547,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -564,6 +564,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -908,7 +911,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q1004"/>
@@ -982,7 +985,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="14.25" hidden="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:17" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>46089</v>
       </c>
@@ -1014,12 +1017,12 @@
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
     </row>
-    <row r="3" spans="1:17" ht="14.25" hidden="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:17" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>46093</v>
       </c>
       <c r="B3" s="3" t="str">
-        <f t="shared" ref="B3:B64" si="0">IF(A3="","",CHOOSE(WEEKDAY(A3,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
+        <f>IF(A3="","",CHOOSE(WEEKDAY(A3,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Torsdag</v>
       </c>
       <c r="C3" s="4"/>
@@ -1049,7 +1052,7 @@
         <v>46094</v>
       </c>
       <c r="B4" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A4="","",CHOOSE(WEEKDAY(A4,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Fredag</v>
       </c>
       <c r="C4" s="4"/>
@@ -1079,7 +1082,7 @@
         <v>46096</v>
       </c>
       <c r="B5" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A5="","",CHOOSE(WEEKDAY(A5,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Söndag</v>
       </c>
       <c r="C5" s="4"/>
@@ -1109,7 +1112,7 @@
         <v>46109</v>
       </c>
       <c r="B6" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A6="","",CHOOSE(WEEKDAY(A6,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Lördag</v>
       </c>
       <c r="C6" s="4"/>
@@ -1134,12 +1137,12 @@
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
     </row>
-    <row r="7" spans="1:17" ht="14.25" hidden="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:17" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
         <v>46112</v>
       </c>
       <c r="B7" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A7="","",CHOOSE(WEEKDAY(A7,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Tisdag</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -1179,7 +1182,7 @@
         <v>46119</v>
       </c>
       <c r="B8" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A8="","",CHOOSE(WEEKDAY(A8,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Tisdag</v>
       </c>
       <c r="C8" s="3" t="s">
@@ -1223,12 +1226,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="14.25" hidden="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:17" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A9" s="2">
         <v>46120</v>
       </c>
       <c r="B9" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A9="","",CHOOSE(WEEKDAY(A9,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Onsdag</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -1273,7 +1276,7 @@
         <v>46121</v>
       </c>
       <c r="B10" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A10="","",CHOOSE(WEEKDAY(A10,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Torsdag</v>
       </c>
       <c r="C10" s="3" t="s">
@@ -1313,12 +1316,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="14.25" hidden="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:17" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A11" s="2">
         <v>46126</v>
       </c>
       <c r="B11" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A11="","",CHOOSE(WEEKDAY(A11,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Tisdag</v>
       </c>
       <c r="C11" s="3" t="s">
@@ -1365,7 +1368,7 @@
         <v>46128</v>
       </c>
       <c r="B12" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A12="","",CHOOSE(WEEKDAY(A12,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Torsdag</v>
       </c>
       <c r="C12" s="3" t="s">
@@ -1410,7 +1413,7 @@
         <v>46130</v>
       </c>
       <c r="B13" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A13="","",CHOOSE(WEEKDAY(A13,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Lördag</v>
       </c>
       <c r="C13" s="3" t="s">
@@ -1456,7 +1459,7 @@
         <v>46134</v>
       </c>
       <c r="B14" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A14="","",CHOOSE(WEEKDAY(A14,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Onsdag</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1498,7 +1501,7 @@
         <v>46136</v>
       </c>
       <c r="B15" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A15="","",CHOOSE(WEEKDAY(A15,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Fredag</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -1542,12 +1545,12 @@
         <v>73</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="14.25" hidden="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:17" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A16" s="2">
         <v>46140</v>
       </c>
       <c r="B16" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A16="","",CHOOSE(WEEKDAY(A16,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Tisdag</v>
       </c>
       <c r="C16" s="3" t="s">
@@ -1588,7 +1591,7 @@
         <v>46141</v>
       </c>
       <c r="B17" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A17="","",CHOOSE(WEEKDAY(A17,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Onsdag</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -1630,7 +1633,7 @@
         <v>46144</v>
       </c>
       <c r="B18" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A18="","",CHOOSE(WEEKDAY(A18,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Lördag</v>
       </c>
       <c r="C18" s="6">
@@ -1667,12 +1670,12 @@
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
     </row>
-    <row r="19" spans="1:16" ht="14.25" hidden="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:16" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A19" s="2">
         <v>46147</v>
       </c>
       <c r="B19" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A19="","",CHOOSE(WEEKDAY(A19,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Tisdag</v>
       </c>
       <c r="C19" s="3" t="s">
@@ -1715,7 +1718,7 @@
         <v>46148</v>
       </c>
       <c r="B20" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A20="","",CHOOSE(WEEKDAY(A20,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Onsdag</v>
       </c>
       <c r="C20" s="6">
@@ -1757,7 +1760,7 @@
         <v>46149</v>
       </c>
       <c r="B21" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A21="","",CHOOSE(WEEKDAY(A21,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Torsdag</v>
       </c>
       <c r="C21" s="3" t="s">
@@ -1794,12 +1797,12 @@
       <c r="N21" s="4"/>
       <c r="O21" s="4"/>
     </row>
-    <row r="22" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="2">
         <v>46153</v>
       </c>
       <c r="B22" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A22="","",CHOOSE(WEEKDAY(A22,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Måndag</v>
       </c>
       <c r="C22" s="6">
@@ -1841,7 +1844,7 @@
         <v>46153</v>
       </c>
       <c r="B23" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A23="","",CHOOSE(WEEKDAY(A23,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Måndag</v>
       </c>
       <c r="C23" s="6">
@@ -1888,7 +1891,7 @@
         <v>46157</v>
       </c>
       <c r="B24" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A24="","",CHOOSE(WEEKDAY(A24,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Fredag</v>
       </c>
       <c r="C24" s="3" t="s">
@@ -1928,12 +1931,12 @@
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="2">
         <v>46160</v>
       </c>
       <c r="B25" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A25="","",CHOOSE(WEEKDAY(A25,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Måndag</v>
       </c>
       <c r="C25" s="3" t="s">
@@ -1973,7 +1976,7 @@
         <v>46162</v>
       </c>
       <c r="B26" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A26="","",CHOOSE(WEEKDAY(A26,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Onsdag</v>
       </c>
       <c r="C26" s="3" t="s">
@@ -2015,7 +2018,7 @@
         <v>46163</v>
       </c>
       <c r="B27" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A27="","",CHOOSE(WEEKDAY(A27,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Torsdag</v>
       </c>
       <c r="C27" s="3" t="s">
@@ -2057,7 +2060,7 @@
         <v>46168</v>
       </c>
       <c r="B28" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A28="","",CHOOSE(WEEKDAY(A28,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Tisdag</v>
       </c>
       <c r="C28" s="6">
@@ -2098,12 +2101,12 @@
       </c>
       <c r="O28" s="3"/>
     </row>
-    <row r="29" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="2">
         <v>46170</v>
       </c>
       <c r="B29" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A29="","",CHOOSE(WEEKDAY(A29,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Torsdag</v>
       </c>
       <c r="C29" s="3" t="s">
@@ -2143,7 +2146,7 @@
         <v>46171</v>
       </c>
       <c r="B30" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A30="","",CHOOSE(WEEKDAY(A30,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Fredag</v>
       </c>
       <c r="C30" s="3" t="s">
@@ -2180,12 +2183,12 @@
       <c r="N30" s="4"/>
       <c r="O30" s="4"/>
     </row>
-    <row r="31" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="2">
         <v>46175</v>
       </c>
       <c r="B31" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A31="","",CHOOSE(WEEKDAY(A31,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Tisdag</v>
       </c>
       <c r="C31" s="3" t="s">
@@ -2225,7 +2228,7 @@
         <v>46180</v>
       </c>
       <c r="B32" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A32="","",CHOOSE(WEEKDAY(A32,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Söndag</v>
       </c>
       <c r="C32" s="3" t="s">
@@ -2265,12 +2268,12 @@
         <v>99</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="2">
         <v>46186</v>
       </c>
       <c r="B33" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A33="","",CHOOSE(WEEKDAY(A33,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Lördag</v>
       </c>
       <c r="C33" s="3"/>
@@ -2294,12 +2297,12 @@
       <c r="O33" s="3"/>
       <c r="P33" s="3"/>
     </row>
-    <row r="34" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="2">
         <v>46187</v>
       </c>
       <c r="B34" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A34="","",CHOOSE(WEEKDAY(A34,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Söndag</v>
       </c>
       <c r="C34" s="3"/>
@@ -2323,12 +2326,12 @@
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
     </row>
-    <row r="35" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="2">
         <v>46188</v>
       </c>
       <c r="B35" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A35="","",CHOOSE(WEEKDAY(A35,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Måndag</v>
       </c>
       <c r="C35" s="3"/>
@@ -2352,12 +2355,12 @@
       <c r="O35" s="3"/>
       <c r="P35" s="3"/>
     </row>
-    <row r="36" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="2">
         <v>46189</v>
       </c>
       <c r="B36" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A36="","",CHOOSE(WEEKDAY(A36,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Tisdag</v>
       </c>
       <c r="C36" s="3" t="s">
@@ -2395,12 +2398,12 @@
         <v>119</v>
       </c>
     </row>
-    <row r="37" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="2">
         <v>46196</v>
       </c>
       <c r="B37" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A37="","",CHOOSE(WEEKDAY(A37,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Tisdag</v>
       </c>
       <c r="C37" s="3" t="s">
@@ -2438,12 +2441,12 @@
         <v>99</v>
       </c>
     </row>
-    <row r="38" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="2">
         <v>46245</v>
       </c>
       <c r="B38" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A38="","",CHOOSE(WEEKDAY(A38,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Tisdag</v>
       </c>
       <c r="C38" s="3" t="s">
@@ -2483,7 +2486,7 @@
         <v>46252</v>
       </c>
       <c r="B39" s="11" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A39="","",CHOOSE(WEEKDAY(A39,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Tisdag</v>
       </c>
       <c r="C39" s="11" t="s">
@@ -2522,12 +2525,12 @@
       <c r="P39" s="7"/>
       <c r="Q39" s="7"/>
     </row>
-    <row r="40" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="2">
         <v>46257</v>
       </c>
       <c r="B40" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A40="","",CHOOSE(WEEKDAY(A40,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Söndag</v>
       </c>
       <c r="C40" s="3" t="s">
@@ -2565,43 +2568,45 @@
         <v>102</v>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="9">
-        <v>46265</v>
+        <v>46260</v>
       </c>
       <c r="B41" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>Måndag</v>
+        <f>IF(A41="","",CHOOSE(WEEKDAY(A41,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
+        <v>Onsdag</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F41" s="11">
-        <v>60220093</v>
+        <v>60713048</v>
       </c>
       <c r="G41" s="11">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>50</v>
+        <v>106</v>
       </c>
       <c r="K41" s="11" t="b">
         <v>1</v>
       </c>
       <c r="L41" s="13"/>
-      <c r="M41" s="13"/>
+      <c r="M41" s="11" t="s">
+        <v>46</v>
+      </c>
       <c r="N41" s="13"/>
       <c r="O41" s="13"/>
       <c r="P41" s="7"/>
@@ -2609,94 +2614,92 @@
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B42" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Onsdag</v>
+        <f>IF(A42="","",CHOOSE(WEEKDAY(A42,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
+        <v>Torsdag</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F42" s="3">
-        <v>60713048</v>
+        <v>60716048</v>
       </c>
       <c r="G42" s="3">
         <v>12</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>106</v>
+        <v>50</v>
       </c>
       <c r="K42" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L42" s="4"/>
       <c r="M42" s="3" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="N42" s="4"/>
       <c r="O42" s="4"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A43" s="2">
-        <v>46261</v>
-      </c>
-      <c r="B43" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Torsdag</v>
-      </c>
-      <c r="C43" s="3" t="s">
+      <c r="A43" s="14">
+        <v>46265</v>
+      </c>
+      <c r="B43" s="15" t="str">
+        <f>IF(A43="","",CHOOSE(WEEKDAY(A43,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
+        <v>Måndag</v>
+      </c>
+      <c r="C43" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F43" s="3">
-        <v>60716048</v>
-      </c>
-      <c r="G43" s="3">
-        <v>12</v>
-      </c>
-      <c r="H43" s="3" t="s">
+      <c r="D43" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E43" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="F43" s="15">
+        <v>60220093</v>
+      </c>
+      <c r="G43" s="15">
+        <v>16</v>
+      </c>
+      <c r="H43" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="J43" s="3" t="s">
+      <c r="I43" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="J43" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="K43" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L43" s="4"/>
-      <c r="M43" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="N43" s="4"/>
-      <c r="O43" s="4"/>
+      <c r="K43" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="L43" s="16"/>
+      <c r="M43" s="16"/>
+      <c r="N43" s="16"/>
+      <c r="O43" s="16"/>
     </row>
     <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" s="2">
         <v>46266</v>
       </c>
       <c r="B44" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A44="","",CHOOSE(WEEKDAY(A44,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Tisdag</v>
       </c>
       <c r="C44" s="3" t="s">
@@ -2740,7 +2743,7 @@
         <v>46267</v>
       </c>
       <c r="B45" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A45="","",CHOOSE(WEEKDAY(A45,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Onsdag</v>
       </c>
       <c r="C45" s="3" t="s">
@@ -2779,12 +2782,12 @@
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="2">
         <v>46271</v>
       </c>
       <c r="B46" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A46="","",CHOOSE(WEEKDAY(A46,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Söndag</v>
       </c>
       <c r="C46" s="3" t="s">
@@ -2824,7 +2827,7 @@
         <v>46273</v>
       </c>
       <c r="B47" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A47="","",CHOOSE(WEEKDAY(A47,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Tisdag</v>
       </c>
       <c r="C47" s="3" t="s">
@@ -2868,7 +2871,7 @@
         <v>46275</v>
       </c>
       <c r="B48" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A48="","",CHOOSE(WEEKDAY(A48,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Torsdag</v>
       </c>
       <c r="C48" s="3" t="s">
@@ -2907,37 +2910,37 @@
       <c r="N48" s="3"/>
       <c r="O48" s="3"/>
     </row>
-    <row r="49" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" s="2">
-        <v>46387</v>
+        <v>46281</v>
       </c>
       <c r="B49" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Torsdag</v>
+        <f>IF(A49="","",CHOOSE(WEEKDAY(A49,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
+        <v>Onsdag</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F49" s="3">
-        <v>60220113</v>
+        <v>60713060</v>
       </c>
       <c r="G49" s="3">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K49" s="3" t="b">
         <v>1</v>
@@ -2945,7 +2948,9 @@
       <c r="L49" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="M49" s="3"/>
+      <c r="M49" s="3" t="s">
+        <v>46</v>
+      </c>
       <c r="N49" s="3"/>
       <c r="O49" s="3" t="s">
         <v>6</v>
@@ -2953,23 +2958,23 @@
     </row>
     <row r="50" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" s="2">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="B50" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Onsdag</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>40</v>
+        <f>IF(A50="","",CHOOSE(WEEKDAY(A50,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
+        <v>Fredag</v>
+      </c>
+      <c r="C50" s="6">
+        <v>0.84375</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F50" s="3">
-        <v>60713060</v>
+        <v>60716058</v>
       </c>
       <c r="G50" s="3">
         <v>15</v>
@@ -2978,35 +2983,33 @@
         <v>23</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K50" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" s="3" t="s">
         <v>45</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="N50" s="3"/>
-      <c r="O50" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="O50" s="3"/>
     </row>
     <row r="51" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" s="2">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="B51" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A51="","",CHOOSE(WEEKDAY(A51,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Fredag</v>
       </c>
-      <c r="C51" s="6">
-        <v>0.84375</v>
+      <c r="C51" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>53</v>
@@ -3015,42 +3018,40 @@
         <v>54</v>
       </c>
       <c r="F51" s="3">
-        <v>60716058</v>
+        <v>60716062</v>
       </c>
       <c r="G51" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="K51" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L51" s="3" t="s">
-        <v>45</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L51" s="4"/>
       <c r="M51" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="N51" s="3"/>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+        <v>60</v>
+      </c>
+      <c r="N51" s="4"/>
+      <c r="O51" s="4"/>
+    </row>
+    <row r="52" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" s="2">
-        <v>46287</v>
+        <v>46295</v>
       </c>
       <c r="B52" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Tisdag</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>48</v>
+        <f>IF(A52="","",CHOOSE(WEEKDAY(A52,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
+        <v>Onsdag</v>
+      </c>
+      <c r="C52" s="8">
+        <v>0.84375</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>36</v>
@@ -3059,38 +3060,40 @@
         <v>37</v>
       </c>
       <c r="F52" s="3">
-        <v>60220119</v>
+        <v>60220066</v>
       </c>
       <c r="G52" s="3">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="K52" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L52" s="4"/>
-      <c r="M52" s="4"/>
-      <c r="N52" s="4"/>
-      <c r="O52" s="4"/>
+      <c r="L52" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="M52" s="3"/>
+      <c r="N52" s="3"/>
+      <c r="O52" s="3"/>
     </row>
     <row r="53" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A53" s="2">
-        <v>46316</v>
+        <v>46297</v>
       </c>
       <c r="B53" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Onsdag</v>
+        <f>IF(A53="","",CHOOSE(WEEKDAY(A53,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
+        <v>Fredag</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>41</v>
@@ -3099,40 +3102,44 @@
         <v>42</v>
       </c>
       <c r="F53" s="3">
-        <v>60713064</v>
+        <v>60713066</v>
       </c>
       <c r="G53" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="K53" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L53" s="4"/>
+      <c r="L53" s="3" t="s">
+        <v>45</v>
+      </c>
       <c r="M53" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="N53" s="4"/>
-      <c r="O53" s="4"/>
+        <v>70</v>
+      </c>
+      <c r="N53" s="3"/>
+      <c r="O53" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="54" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A54" s="2">
-        <v>46290</v>
+        <v>46297</v>
       </c>
       <c r="B54" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A54="","",CHOOSE(WEEKDAY(A54,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v>Fredag</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>48</v>
+        <v>113</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>53</v>
@@ -3141,40 +3148,44 @@
         <v>54</v>
       </c>
       <c r="F54" s="3">
-        <v>60716062</v>
+        <v>60716068</v>
       </c>
       <c r="G54" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>50</v>
+        <v>114</v>
       </c>
       <c r="K54" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L54" s="4"/>
+      <c r="L54" s="3" t="s">
+        <v>45</v>
+      </c>
       <c r="M54" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="N54" s="4"/>
-      <c r="O54" s="4"/>
-    </row>
-    <row r="55" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+        <v>64</v>
+      </c>
+      <c r="N54" s="3"/>
+      <c r="O54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A55" s="2">
-        <v>46295</v>
+        <v>46299</v>
       </c>
       <c r="B55" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Onsdag</v>
-      </c>
-      <c r="C55" s="8">
-        <v>0.84375</v>
+        <f>IF(A55="","",CHOOSE(WEEKDAY(A55,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
+        <v>Söndag</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>116</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>36</v>
@@ -3183,40 +3194,38 @@
         <v>37</v>
       </c>
       <c r="F55" s="3">
-        <v>60220066</v>
+        <v>60220122</v>
       </c>
       <c r="G55" s="3">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="K55" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L55" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="M55" s="3"/>
-      <c r="N55" s="3"/>
-      <c r="O55" s="3"/>
+      <c r="L55" s="4"/>
+      <c r="M55" s="4"/>
+      <c r="N55" s="4"/>
+      <c r="O55" s="4"/>
     </row>
     <row r="56" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A56" s="2">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="B56" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Fredag</v>
+        <f>IF(A56="","",CHOOSE(WEEKDAY(A56,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
+        <v>Tisdag</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>53</v>
@@ -3225,65 +3234,61 @@
         <v>54</v>
       </c>
       <c r="F56" s="3">
-        <v>60716068</v>
+        <v>60716069</v>
       </c>
       <c r="G56" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>114</v>
+        <v>50</v>
       </c>
       <c r="K56" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L56" s="3" t="s">
-        <v>45</v>
-      </c>
+      <c r="L56" s="4"/>
       <c r="M56" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="N56" s="3"/>
-      <c r="O56" s="3" t="s">
-        <v>5</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="N56" s="4"/>
+      <c r="O56" s="4"/>
     </row>
     <row r="57" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A57" s="2">
-        <v>46297</v>
+        <v>46302</v>
       </c>
       <c r="B57" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Fredag</v>
+        <f>IF(A57="","",CHOOSE(WEEKDAY(A57,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
+        <v>Onsdag</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F57" s="3">
-        <v>60713066</v>
+        <v>60220113</v>
       </c>
       <c r="G57" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K57" s="3" t="b">
         <v>1</v>
@@ -3291,82 +3296,82 @@
       <c r="L57" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>70</v>
-      </c>
+      <c r="M57" s="3"/>
       <c r="N57" s="3"/>
       <c r="O57" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A58" s="2">
-        <v>46299</v>
+        <v>46303</v>
       </c>
       <c r="B58" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Söndag</v>
+        <f>IF(A58="","",CHOOSE(WEEKDAY(A58,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
+        <v>Torsdag</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>116</v>
+        <v>48</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F58" s="3">
-        <v>60220122</v>
+        <v>60713071</v>
       </c>
       <c r="G58" s="3">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>94</v>
+        <v>43</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>117</v>
+        <v>50</v>
       </c>
       <c r="K58" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L58" s="4"/>
-      <c r="M58" s="4"/>
+      <c r="M58" s="3" t="s">
+        <v>46</v>
+      </c>
       <c r="N58" s="4"/>
       <c r="O58" s="4"/>
     </row>
     <row r="59" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A59" s="2">
-        <v>46301</v>
+        <v>46303</v>
       </c>
       <c r="B59" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Tisdag</v>
+        <f>IF(A59="","",CHOOSE(WEEKDAY(A59,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
+        <v>Torsdag</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>48</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F59" s="3">
-        <v>60716069</v>
+        <v>60220119</v>
       </c>
       <c r="G59" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>29</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>50</v>
@@ -3375,40 +3380,38 @@
         <v>1</v>
       </c>
       <c r="L59" s="4"/>
-      <c r="M59" s="3" t="s">
-        <v>78</v>
-      </c>
+      <c r="M59" s="4"/>
       <c r="N59" s="4"/>
       <c r="O59" s="4"/>
     </row>
     <row r="60" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A60" s="2">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="B60" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Torsdag</v>
+        <f>IF(A60="","",CHOOSE(WEEKDAY(A60,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
+        <v>Söndag</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>48</v>
+        <v>118</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F60" s="3">
-        <v>60713071</v>
+        <v>60220132</v>
       </c>
       <c r="G60" s="3">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>29</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>50</v>
@@ -3417,40 +3420,38 @@
         <v>1</v>
       </c>
       <c r="L60" s="4"/>
-      <c r="M60" s="3" t="s">
-        <v>46</v>
-      </c>
+      <c r="M60" s="4"/>
       <c r="N60" s="4"/>
       <c r="O60" s="4"/>
     </row>
-    <row r="61" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A61" s="2">
-        <v>46306</v>
+        <v>46316</v>
       </c>
       <c r="B61" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Söndag</v>
+        <f>IF(A61="","",CHOOSE(WEEKDAY(A61,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
+        <v>Onsdag</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>118</v>
+        <v>48</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F61" s="3">
-        <v>60220132</v>
+        <v>60713064</v>
       </c>
       <c r="G61" s="3">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>29</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="J61" s="3" t="s">
         <v>50</v>
@@ -3459,14 +3460,16 @@
         <v>1</v>
       </c>
       <c r="L61" s="4"/>
-      <c r="M61" s="4"/>
+      <c r="M61" s="3" t="s">
+        <v>67</v>
+      </c>
       <c r="N61" s="4"/>
       <c r="O61" s="4"/>
     </row>
-    <row r="62" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A62" s="10"/>
       <c r="B62" s="12" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A62="","",CHOOSE(WEEKDAY(A62,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v/>
       </c>
       <c r="C62" s="12"/>
@@ -3483,10 +3486,10 @@
       <c r="N62" s="12"/>
       <c r="O62" s="12"/>
     </row>
-    <row r="63" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A63" s="2"/>
       <c r="B63" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A63="","",CHOOSE(WEEKDAY(A63,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v/>
       </c>
       <c r="C63" s="3"/>
@@ -3499,10 +3502,10 @@
       <c r="J63" s="3"/>
       <c r="K63" s="3"/>
     </row>
-    <row r="64" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="10"/>
       <c r="B64" s="12" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A64="","",CHOOSE(WEEKDAY(A64,2),"Måndag","Tisdag","Onsdag","Torsdag","Fredag","Lördag","Söndag"))</f>
         <v/>
       </c>
       <c r="C64" s="12"/>
@@ -4461,65 +4464,59 @@
     <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <autoFilter ref="A1:O64" xr:uid="{00000000-0009-0000-0000-000001000000}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="Svart"/>
-        <filter val="Vit"/>
-      </filters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O64">
       <sortCondition ref="A1:A64"/>
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A2:O33 P8:P9 P11:P12 P15:P16 P32:P35 A34:D35 F34:O35 A36:O64">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>$O2="ALLA TRE (DAM+VIT+SVART)"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="2">
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>$O2="DAM-VIT"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="3">
+    <cfRule type="expression" dxfId="5" priority="3">
       <formula>$O2="DAM-SVART"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="4">
+    <cfRule type="expression" dxfId="4" priority="4">
       <formula>$O2="VIT-SVART"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="5">
+    <cfRule type="expression" dxfId="3" priority="5">
       <formula>AND($O2&lt;&gt;"",ISNUMBER(SEARCH(",",$O2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="6">
+    <cfRule type="expression" dxfId="2" priority="6">
       <formula>$D2="Dam"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="7">
+    <cfRule type="expression" dxfId="1" priority="7">
       <formula>$D2="Vit"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="8">
+    <cfRule type="expression" dxfId="0" priority="8">
       <formula>$D2="Svart"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E34:E35">
-    <cfRule type="expression" dxfId="7" priority="25">
+    <cfRule type="expression" dxfId="15" priority="25">
       <formula>$O33="ALLA TRE (DAM+VIT+SVART)"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="26">
+    <cfRule type="expression" dxfId="14" priority="26">
       <formula>$O33="DAM-VIT"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="27">
+    <cfRule type="expression" dxfId="13" priority="27">
       <formula>$O33="DAM-SVART"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="28">
+    <cfRule type="expression" dxfId="12" priority="28">
       <formula>$O33="VIT-SVART"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="29">
+    <cfRule type="expression" dxfId="11" priority="29">
       <formula>AND($O33&lt;&gt;"",ISNUMBER(SEARCH(",",$O33)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="30">
+    <cfRule type="expression" dxfId="10" priority="30">
       <formula>$D33="Dam"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="31">
+    <cfRule type="expression" dxfId="9" priority="31">
       <formula>$D33="Vit"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="32">
+    <cfRule type="expression" dxfId="8" priority="32">
       <formula>$D33="Svart"</formula>
     </cfRule>
   </conditionalFormatting>
